--- a/docs/Files/ODYM_Tutorial6_SectorSplit_V1.0_EVLIB.xlsx
+++ b/docs/Files/ODYM_Tutorial6_SectorSplit_V1.0_EVLIB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB399B1B-54C2-4642-BAE7-787A39EAA40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D85B8B6-0378-4597-816C-850368FB0D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -323,9 +323,6 @@
     <t>Lanphear</t>
   </si>
   <si>
-    <t>ODYM_Classifications_Master_EV_LIB</t>
-  </si>
-  <si>
     <t>LIB</t>
   </si>
   <si>
@@ -336,6 +333,9 @@
   </si>
   <si>
     <t>other EV LIB products</t>
+  </si>
+  <si>
+    <t>ODYM_Classifications_EV_LIB</t>
   </si>
 </sst>
 </file>
@@ -957,7 +957,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
@@ -1176,10 +1176,13 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>102</v>
+      </c>
+      <c r="D2">
+        <v>0.439873417721519</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1196,10 +1199,13 @@
         <v>56</v>
       </c>
       <c r="B3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" t="s">
         <v>102</v>
       </c>
-      <c r="C3" t="s">
-        <v>103</v>
+      <c r="D3">
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1216,10 +1222,13 @@
         <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>103</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1236,10 +1245,13 @@
         <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>103</v>
+      </c>
+      <c r="D5">
+        <v>0.560126582278481</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1256,10 +1268,13 @@
         <v>57</v>
       </c>
       <c r="B6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>102</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1276,10 +1291,13 @@
         <v>57</v>
       </c>
       <c r="B7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" t="s">
         <v>102</v>
       </c>
-      <c r="C7" t="s">
-        <v>103</v>
+      <c r="D7">
+        <v>0.22797927461139897</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1296,10 +1314,13 @@
         <v>57</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>103</v>
+      </c>
+      <c r="D8">
+        <v>0.772020725388601</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1316,10 +1337,13 @@
         <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>103</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
